--- a/marketing_forms/046_personal_styling_questionaire--marketing_forms.xlsx
+++ b/marketing_forms/046_personal_styling_questionaire--marketing_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -730,12 +730,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C18"/>
+  <dimension ref="A1:C16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
-    <col width="35" customWidth="1" min="2" max="2"/>
-    <col width="35" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -763,12 +763,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'style_1'}</t>
+          <t>style_1</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Style 1'}</t>
+          <t>Style 1</t>
         </is>
       </c>
     </row>
@@ -780,12 +780,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'style_2'}</t>
+          <t>style_2</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Style 2'}</t>
+          <t>Style 2</t>
         </is>
       </c>
     </row>
@@ -797,12 +797,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'style_3'}</t>
+          <t>style_3</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Style 3'}</t>
+          <t>Style 3</t>
         </is>
       </c>
     </row>
@@ -814,12 +814,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'theme_goals'}</t>
+          <t>theme_goals</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Theme_goals'}</t>
+          <t>Theme goals</t>
         </is>
       </c>
     </row>
@@ -831,29 +831,29 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'theme_goals'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Theme_goals'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>party_theme_choices</t>
+          <t>party_size_choices</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'theme_goals'}</t>
+          <t>small</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Theme_goals'}</t>
+          <t>Small</t>
         </is>
       </c>
     </row>
@@ -865,12 +865,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'small'}</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Small'}</t>
+          <t>Medium</t>
         </is>
       </c>
     </row>
@@ -882,29 +882,29 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'medium'}</t>
+          <t>large</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Medium'}</t>
+          <t>Large</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>party_size_choices</t>
+          <t>party_location_choices</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'large'}</t>
+          <t>location_1</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Large'}</t>
+          <t>Location 1</t>
         </is>
       </c>
     </row>
@@ -916,12 +916,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'location_1'}</t>
+          <t>location_2</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Location 1'}</t>
+          <t>Location 2</t>
         </is>
       </c>
     </row>
@@ -933,29 +933,29 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'location_2'}</t>
+          <t>location_3</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Location 2'}</t>
+          <t>Location 3</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>party_location_choices</t>
+          <t>party_details2_choices</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'location_3'}</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Location 3'}</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -967,29 +967,29 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>party_details2_choices</t>
+          <t>party_time2_choices</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>time_1</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Time 1</t>
         </is>
       </c>
     </row>
@@ -1001,46 +1001,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'time_1'}</t>
+          <t>time_2</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Time 1'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>party_time2_choices</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>{'id':_2,_'label':_'time_2'}</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>{'id': 2, 'label': 'Time 2'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>party_time2_choices</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>{'id':_3,_'label':_'time_2'}</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>{'id': 3, 'label': 'Time 2'}</t>
+          <t>Time 2</t>
         </is>
       </c>
     </row>
